--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -29,42 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
     <t>2026-06-23</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-06-24</t>
   </si>
   <si>
@@ -282,6 +252,48 @@
   </si>
   <si>
     <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
   </si>
   <si>
     <t>Reason</t>
@@ -394,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -415,103 +427,103 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>326.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>150.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2681.0</v>
+        <v>2360.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>141.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>3373.0</v>
+        <v>2253.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>141.0</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>3439.0</v>
+        <v>2326.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B5" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>141.0</v>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2790.0</v>
+        <v>2796.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B6" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>141.0</v>
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2704.0</v>
+        <v>2284.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B7" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>141.0</v>
+        <v>10</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2343.0</v>
+        <v>2480.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B8" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C8" t="n" s="0">
-        <v>141.0</v>
+        <v>11</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2337.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>307.0</v>
@@ -520,306 +532,306 @@
         <v>141.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2125.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2512.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2592.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2692.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2360.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2253.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2326.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>2796.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2284.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2480.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2099.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>307.0</v>
+        <v>305.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>141.0</v>
+        <v>132.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2431.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2410.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2299.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2011.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>2011.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2110.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2055.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2135.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2142.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2037.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2248.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>305.0</v>
@@ -828,12 +840,12 @@
         <v>132.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2243.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>305.0</v>
@@ -842,12 +854,12 @@
         <v>132.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2005.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>305.0</v>
@@ -856,166 +868,166 @@
         <v>132.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1742.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1739.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1657.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1634.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1613.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1759.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2493.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2047.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1702.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1497.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1499.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1575.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>329.0</v>
@@ -1024,581 +1036,623 @@
         <v>112.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1574.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1697.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1657.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1598.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1588.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1650.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1619.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1890.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1849.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1497.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1558.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1472.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1458.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>329.0</v>
+        <v>331.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>105.0</v>
+        <v>100.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1557.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1396.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1670.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1546.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1531.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1389.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1282.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1293.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1307.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1414.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1308.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1305.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1237.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1199.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1369.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1467.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1472.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1259.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1254.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1326.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1313.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1391.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1431.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1493.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1343.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1379.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1723.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1552.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>319.0</v>
+        <v>308.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>1408.0</v>
+        <v>1146.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>308.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>985.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>308.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>1036.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>308.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>1067.0</v>
       </c>
     </row>
   </sheetData>
@@ -1613,41 +1667,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>24.0</v>
@@ -1655,41 +1709,41 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1697,27 +1751,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>127.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1725,16 +1779,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -1749,16 +1803,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1773,18 +1827,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,30 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-23</t>
+    <t>2026-06-29</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
     <t>2026-06-30</t>
   </si>
   <si>
@@ -294,6 +276,15 @@
   </si>
   <si>
     <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
   </si>
   <si>
     <t>Reason</t>
@@ -406,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -434,91 +425,91 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2360.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>307.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>141.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2253.0</v>
+        <v>2431.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>127.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2326.0</v>
+        <v>2410.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>5</v>
+      <c r="B5" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>127.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2796.0</v>
+        <v>2299.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+      <c r="B6" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>127.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2284.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>5</v>
+      <c r="B7" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>127.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2480.0</v>
+        <v>2011.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>5</v>
+      <c r="B8" t="n" s="0">
+        <v>302.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>127.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2099.0</v>
+        <v>2110.0</v>
       </c>
     </row>
     <row r="9">
@@ -526,13 +517,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>307.0</v>
+        <v>302.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>141.0</v>
+        <v>127.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2431.0</v>
+        <v>2055.0</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +537,7 @@
         <v>127.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2410.0</v>
+        <v>2135.0</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +551,7 @@
         <v>127.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2299.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +565,7 @@
         <v>127.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2011.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +579,7 @@
         <v>127.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2011.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="14">
@@ -596,13 +587,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2110.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="15">
@@ -610,13 +601,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2055.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="16">
@@ -624,13 +615,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>2135.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="17">
@@ -638,13 +629,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2142.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="18">
@@ -652,13 +643,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2037.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="19">
@@ -666,13 +657,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2248.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="20">
@@ -686,7 +677,7 @@
         <v>132.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2243.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="21">
@@ -700,7 +691,7 @@
         <v>132.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2005.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="22">
@@ -714,7 +705,7 @@
         <v>132.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1742.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +719,7 @@
         <v>132.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1739.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="24">
@@ -742,7 +733,7 @@
         <v>132.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1657.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="25">
@@ -756,7 +747,7 @@
         <v>132.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1634.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="26">
@@ -770,7 +761,7 @@
         <v>132.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1613.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +775,7 @@
         <v>132.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1759.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="28">
@@ -792,13 +783,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2493.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="29">
@@ -806,13 +797,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2047.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="30">
@@ -820,13 +811,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1702.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="31">
@@ -834,13 +825,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1497.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="32">
@@ -848,13 +839,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1499.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="33">
@@ -862,13 +853,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1575.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="34">
@@ -882,7 +873,7 @@
         <v>112.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1574.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="35">
@@ -896,7 +887,7 @@
         <v>112.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1697.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="36">
@@ -910,7 +901,7 @@
         <v>112.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1657.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="37">
@@ -924,7 +915,7 @@
         <v>112.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1598.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="38">
@@ -938,7 +929,7 @@
         <v>112.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1588.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="39">
@@ -952,7 +943,7 @@
         <v>112.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1650.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="40">
@@ -963,10 +954,10 @@
         <v>329.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1619.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="41">
@@ -977,10 +968,10 @@
         <v>329.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1890.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="42">
@@ -988,13 +979,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1849.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="43">
@@ -1002,13 +993,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1497.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="44">
@@ -1016,13 +1007,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1558.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="45">
@@ -1030,13 +1021,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1472.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,13 +1035,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1458.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="47">
@@ -1058,13 +1049,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1557.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="48">
@@ -1072,13 +1063,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1396.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="49">
@@ -1086,13 +1077,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1670.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="50">
@@ -1100,13 +1091,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1546.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="51">
@@ -1114,13 +1105,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1531.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="52">
@@ -1128,13 +1119,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1389.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,13 +1133,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1282.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="54">
@@ -1156,13 +1147,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1293.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="55">
@@ -1170,13 +1161,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1307.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,13 +1175,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1414.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="57">
@@ -1198,13 +1189,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1308.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="58">
@@ -1212,13 +1203,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1305.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="59">
@@ -1226,13 +1217,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1237.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="60">
@@ -1240,13 +1231,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1199.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="61">
@@ -1254,13 +1245,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1369.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1265,7 @@
         <v>100.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1467.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="63">
@@ -1282,13 +1273,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1472.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="64">
@@ -1296,13 +1287,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1259.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="65">
@@ -1310,13 +1301,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1254.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="66">
@@ -1324,13 +1315,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1326.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="67">
@@ -1338,13 +1329,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1313.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="68">
@@ -1352,13 +1343,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1391.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="69">
@@ -1372,7 +1363,7 @@
         <v>102.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1431.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,13 +1371,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1493.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,13 +1385,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1343.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="72">
@@ -1408,13 +1399,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1379.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,13 +1413,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1723.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,13 +1427,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1552.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="75">
@@ -1450,13 +1441,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1408.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="76">
@@ -1470,7 +1461,7 @@
         <v>102.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1468.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="77">
@@ -1484,7 +1475,7 @@
         <v>102.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1477.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="78">
@@ -1498,7 +1489,7 @@
         <v>102.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1447.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="79">
@@ -1512,7 +1503,7 @@
         <v>102.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1252.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="80">
@@ -1520,13 +1511,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1248.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="81">
@@ -1534,13 +1525,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1316.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="82">
@@ -1548,13 +1539,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1305.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="83">
@@ -1562,13 +1553,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1284.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="84">
@@ -1576,13 +1567,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1392.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="85">
@@ -1590,13 +1581,13 @@
         <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>1246.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="86">
@@ -1604,55 +1595,13 @@
         <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>1146.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>985.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>1036.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>1067.0</v>
+        <v>1047.0</v>
       </c>
     </row>
   </sheetData>
@@ -1667,27 +1616,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>114.0</v>
@@ -1695,27 +1644,27 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>11.0</v>
@@ -1723,13 +1672,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>8.0</v>
@@ -1737,13 +1686,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1751,27 +1700,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>115.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1779,16 +1728,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
   </sheetData>
@@ -1803,16 +1752,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1827,18 +1776,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
   <si>
     <t>Date</t>
   </si>
@@ -29,37 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-06-29</t>
+    <t>2026-07-08</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-07-05</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
   </si>
   <si>
     <t>2026-07-09</t>
@@ -397,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -425,21 +398,21 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2099.0</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>141.0</v>
+      <c r="B3" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2431.0</v>
+        <v>2037.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +426,7 @@
         <v>127.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2410.0</v>
+        <v>2248.0</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +434,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2299.0</v>
+        <v>2243.0</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +448,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2011.0</v>
+        <v>2005.0</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +462,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2011.0</v>
+        <v>1742.0</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +476,13 @@
         <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2110.0</v>
+        <v>1739.0</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +490,13 @@
         <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2055.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +504,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2135.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +518,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2142.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="12">
@@ -559,13 +532,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2037.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="13">
@@ -573,13 +546,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>302.0</v>
+        <v>305.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>127.0</v>
+        <v>132.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2248.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="14">
@@ -593,7 +566,7 @@
         <v>132.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2243.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +580,7 @@
         <v>132.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2005.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="16">
@@ -621,7 +594,7 @@
         <v>132.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1742.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="17">
@@ -635,7 +608,7 @@
         <v>132.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1739.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="18">
@@ -649,7 +622,7 @@
         <v>132.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1657.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="19">
@@ -657,13 +630,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1634.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="20">
@@ -671,13 +644,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1613.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="21">
@@ -685,13 +658,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1759.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="22">
@@ -699,13 +672,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2493.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="23">
@@ -713,13 +686,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2047.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="24">
@@ -727,13 +700,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1702.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="25">
@@ -741,13 +714,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1497.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="26">
@@ -755,13 +728,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1499.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="27">
@@ -769,13 +742,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1575.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="28">
@@ -789,7 +762,7 @@
         <v>112.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1574.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="29">
@@ -803,7 +776,7 @@
         <v>112.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1697.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +790,7 @@
         <v>112.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1657.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="31">
@@ -828,10 +801,10 @@
         <v>329.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1598.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +815,10 @@
         <v>329.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1588.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="33">
@@ -853,13 +826,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1650.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="34">
@@ -867,13 +840,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1619.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="35">
@@ -881,13 +854,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1890.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="36">
@@ -895,13 +868,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1849.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="37">
@@ -909,13 +882,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1497.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="38">
@@ -923,13 +896,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1558.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="39">
@@ -937,13 +910,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1472.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="40">
@@ -951,13 +924,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1458.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,13 +938,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1557.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="42">
@@ -979,13 +952,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1396.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="43">
@@ -993,13 +966,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1670.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="44">
@@ -1007,13 +980,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1546.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="45">
@@ -1021,13 +994,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1531.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="46">
@@ -1035,13 +1008,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1389.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,13 +1022,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1282.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,13 +1036,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1293.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="49">
@@ -1077,13 +1050,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1307.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="50">
@@ -1091,13 +1064,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1414.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,13 +1078,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1308.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="52">
@@ -1119,13 +1092,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1305.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="53">
@@ -1133,13 +1106,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C53" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1237.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,13 +1120,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1199.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="55">
@@ -1161,13 +1134,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1369.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="56">
@@ -1175,13 +1148,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1467.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="57">
@@ -1189,13 +1162,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1472.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="58">
@@ -1203,13 +1176,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1259.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="59">
@@ -1217,13 +1190,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1254.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="60">
@@ -1231,13 +1204,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1326.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,13 +1218,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1313.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,13 +1232,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1391.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="63">
@@ -1273,13 +1246,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1431.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="64">
@@ -1287,13 +1260,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1493.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="65">
@@ -1301,13 +1274,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1343.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="66">
@@ -1315,13 +1288,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1379.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="67">
@@ -1329,13 +1302,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1723.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="68">
@@ -1343,13 +1316,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1552.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="69">
@@ -1357,13 +1330,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1408.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="70">
@@ -1377,7 +1350,7 @@
         <v>102.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1468.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="71">
@@ -1385,13 +1358,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1477.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="72">
@@ -1399,13 +1372,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1447.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="73">
@@ -1413,13 +1386,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1252.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="74">
@@ -1427,13 +1400,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1248.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="75">
@@ -1441,13 +1414,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1316.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="76">
@@ -1455,13 +1428,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1305.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="77">
@@ -1469,138 +1442,12 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1284.0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="0">
-        <v>81</v>
-      </c>
-      <c r="B78" t="n" s="0">
-        <v>310.0</v>
-      </c>
-      <c r="C78" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D78" t="n" s="0">
-        <v>1392.0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="B79" t="n" s="0">
-        <v>310.0</v>
-      </c>
-      <c r="C79" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D79" t="n" s="0">
-        <v>1246.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="0">
-        <v>83</v>
-      </c>
-      <c r="B80" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C80" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D80" t="n" s="0">
-        <v>1146.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="B81" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C81" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D81" t="n" s="0">
-        <v>985.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="B82" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C82" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D82" t="n" s="0">
-        <v>1036.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>308.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
-        <v>1067.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
-        <v>1023.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>1021.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>307.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>102.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
         <v>1047.0</v>
       </c>
     </row>
@@ -1616,27 +1463,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>114.0</v>
@@ -1644,13 +1491,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1658,13 +1505,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>11.0</v>
@@ -1672,13 +1519,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>8.0</v>
@@ -1686,13 +1533,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1700,13 +1547,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n" s="0">
         <v>112.0</v>
@@ -1714,13 +1561,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>104</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1728,13 +1575,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>34.0</v>
@@ -1752,16 +1599,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1776,18 +1623,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -29,36 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-08</t>
+    <t>2026-07-16</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>2026-07-11</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
     <t>2026-07-17</t>
   </si>
   <si>
@@ -258,6 +234,60 @@
   </si>
   <si>
     <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
+  </si>
+  <si>
+    <t>2026-10-04</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
   </si>
   <si>
     <t>Reason</t>
@@ -370,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -398,7 +428,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2142.0</v>
+        <v>1634.0</v>
       </c>
     </row>
     <row r="3">
@@ -412,91 +442,91 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2037.0</v>
+        <v>1613.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>302.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>127.0</v>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2248.0</v>
+        <v>1759.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B5" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>132.0</v>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2243.0</v>
+        <v>2493.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B6" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>132.0</v>
+      <c r="B6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2005.0</v>
+        <v>2047.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B7" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>132.0</v>
+      <c r="B7" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1742.0</v>
+        <v>1702.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C8" t="n" s="0">
-        <v>132.0</v>
+      <c r="B8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1739.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B9" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C9" t="n" s="0">
-        <v>132.0</v>
+      <c r="B9" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1657.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="10">
@@ -510,7 +540,7 @@
         <v>132.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1634.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="11">
@@ -518,13 +548,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1613.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="12">
@@ -532,13 +562,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1759.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="13">
@@ -546,13 +576,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2493.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="14">
@@ -560,13 +590,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2047.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +604,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1702.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="16">
@@ -588,13 +618,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1497.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="17">
@@ -602,13 +632,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1499.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="18">
@@ -616,13 +646,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1575.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="19">
@@ -636,7 +666,7 @@
         <v>112.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1574.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="20">
@@ -650,7 +680,7 @@
         <v>112.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1697.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="21">
@@ -664,7 +694,7 @@
         <v>112.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1657.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +708,7 @@
         <v>112.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1598.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="23">
@@ -689,10 +719,10 @@
         <v>329.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1588.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="24">
@@ -703,10 +733,10 @@
         <v>329.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1650.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="25">
@@ -714,13 +744,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1619.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="26">
@@ -728,13 +758,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1890.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="27">
@@ -742,13 +772,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1849.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="28">
@@ -756,13 +786,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1497.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="29">
@@ -770,13 +800,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1558.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="30">
@@ -784,13 +814,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1472.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="31">
@@ -798,13 +828,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1458.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="32">
@@ -812,13 +842,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1557.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="33">
@@ -826,13 +856,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1396.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="34">
@@ -840,13 +870,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1670.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="35">
@@ -854,13 +884,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>335.0</v>
+        <v>331.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1546.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="36">
@@ -868,13 +898,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1531.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="37">
@@ -882,13 +912,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1389.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="38">
@@ -896,13 +926,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1282.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="39">
@@ -910,13 +940,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>332.0</v>
+        <v>329.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1293.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="40">
@@ -924,13 +954,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1307.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="41">
@@ -938,13 +968,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1414.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="42">
@@ -952,13 +982,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1308.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="43">
@@ -966,13 +996,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1305.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="44">
@@ -980,13 +1010,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1237.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="45">
@@ -994,13 +1024,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1199.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="46">
@@ -1008,13 +1038,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>331.0</v>
+        <v>319.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1369.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="47">
@@ -1022,13 +1052,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1467.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="48">
@@ -1036,13 +1066,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1472.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="49">
@@ -1050,13 +1080,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1259.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="50">
@@ -1064,13 +1094,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1254.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="51">
@@ -1078,13 +1108,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1326.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="52">
@@ -1092,13 +1122,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1313.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="53">
@@ -1106,13 +1136,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>329.0</v>
+        <v>310.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1391.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="54">
@@ -1120,13 +1150,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C54" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1431.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="55">
@@ -1134,13 +1164,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C55" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1493.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="56">
@@ -1148,13 +1178,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C56" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1343.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="57">
@@ -1162,13 +1192,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C57" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1379.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="58">
@@ -1176,13 +1206,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1723.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="59">
@@ -1190,13 +1220,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1552.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="60">
@@ -1204,13 +1234,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1408.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="61">
@@ -1224,7 +1254,7 @@
         <v>102.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1468.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="62">
@@ -1238,7 +1268,7 @@
         <v>102.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1477.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="63">
@@ -1246,13 +1276,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1447.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="64">
@@ -1260,13 +1290,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1252.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="65">
@@ -1274,13 +1304,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1248.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="66">
@@ -1288,13 +1318,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1316.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="67">
@@ -1302,13 +1332,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1305.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="68">
@@ -1316,13 +1346,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1284.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="69">
@@ -1330,13 +1360,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1392.0</v>
+        <v>1047.0</v>
       </c>
     </row>
     <row r="70">
@@ -1344,13 +1374,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>310.0</v>
+        <v>300.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1246.0</v>
+        <v>1043.0</v>
       </c>
     </row>
     <row r="71">
@@ -1358,13 +1388,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1146.0</v>
+        <v>948.0</v>
       </c>
     </row>
     <row r="72">
@@ -1372,13 +1402,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>985.0</v>
+        <v>1196.0</v>
       </c>
     </row>
     <row r="73">
@@ -1386,13 +1416,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1036.0</v>
+        <v>1123.0</v>
       </c>
     </row>
     <row r="74">
@@ -1400,13 +1430,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1067.0</v>
+        <v>1192.0</v>
       </c>
     </row>
     <row r="75">
@@ -1414,13 +1444,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1023.0</v>
+        <v>1136.0</v>
       </c>
     </row>
     <row r="76">
@@ -1428,13 +1458,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1021.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="77">
@@ -1442,13 +1472,153 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1047.0</v>
+        <v>1006.0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="C78" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D78" t="n" s="0">
+        <v>1074.0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="C79" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D79" t="n" s="0">
+        <v>974.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="C80" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D80" t="n" s="0">
+        <v>945.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="C81" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>1046.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B82" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="C82" t="n" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>1105.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>294.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>103.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>861.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>294.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>103.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>938.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>294.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>103.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>950.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>294.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>103.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>935.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>294.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>103.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>950.0</v>
       </c>
     </row>
   </sheetData>
@@ -1463,41 +1633,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>114.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1505,27 +1675,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>8.0</v>
@@ -1533,13 +1703,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1547,27 +1717,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>112.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1575,16 +1745,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
     </row>
   </sheetData>
@@ -1599,16 +1769,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1623,18 +1793,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -29,30 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-16</t>
+    <t>2026-07-22</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>2026-07-19</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
     <t>2026-07-23</t>
   </si>
   <si>
@@ -288,6 +270,15 @@
   </si>
   <si>
     <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-10-11</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>Reason</t>
@@ -400,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -428,7 +419,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1634.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="3">
@@ -442,91 +433,91 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1613.0</v>
+        <v>1499.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+      <c r="B4" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>132.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1759.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>5</v>
+      <c r="B5" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2493.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+      <c r="B6" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2047.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>5</v>
+      <c r="B7" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1702.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>5</v>
+      <c r="B8" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1497.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>5</v>
+      <c r="B9" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1499.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="10">
@@ -534,13 +525,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1575.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="11">
@@ -554,7 +545,7 @@
         <v>112.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1574.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="12">
@@ -568,7 +559,7 @@
         <v>112.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1697.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="13">
@@ -582,7 +573,7 @@
         <v>112.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>1657.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="14">
@@ -596,7 +587,7 @@
         <v>112.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1598.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="15">
@@ -610,7 +601,7 @@
         <v>112.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1588.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="16">
@@ -624,7 +615,7 @@
         <v>112.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1650.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="17">
@@ -635,10 +626,10 @@
         <v>329.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1619.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="18">
@@ -649,10 +640,10 @@
         <v>329.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1890.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="19">
@@ -660,13 +651,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1849.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="20">
@@ -674,13 +665,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1497.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="21">
@@ -688,13 +679,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1558.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="22">
@@ -702,13 +693,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>112.0</v>
+        <v>101.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1472.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="23">
@@ -716,13 +707,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1458.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="24">
@@ -730,13 +721,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>329.0</v>
+        <v>332.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>105.0</v>
+        <v>101.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1557.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="25">
@@ -744,13 +735,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1396.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="26">
@@ -758,13 +749,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1670.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="27">
@@ -772,13 +763,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>335.0</v>
+        <v>330.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1546.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="28">
@@ -786,13 +777,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1531.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="29">
@@ -800,13 +791,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1389.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="30">
@@ -814,13 +805,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1282.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="31">
@@ -828,13 +819,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>332.0</v>
+        <v>331.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1293.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="32">
@@ -842,13 +833,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1307.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="33">
@@ -856,13 +847,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1414.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="34">
@@ -870,13 +861,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>330.0</v>
+        <v>329.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1308.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="35">
@@ -884,13 +875,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C35" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1305.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="36">
@@ -898,13 +889,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C36" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1237.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="37">
@@ -912,13 +903,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C37" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1199.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="38">
@@ -926,13 +917,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C38" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1369.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="39">
@@ -946,7 +937,7 @@
         <v>100.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1467.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="40">
@@ -954,13 +945,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1472.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="41">
@@ -968,13 +959,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1259.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="42">
@@ -982,13 +973,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1254.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="43">
@@ -996,13 +987,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1326.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="44">
@@ -1010,13 +1001,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1313.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="45">
@@ -1024,13 +1015,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1391.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="46">
@@ -1044,7 +1035,7 @@
         <v>102.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1431.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="47">
@@ -1052,13 +1043,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1493.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="48">
@@ -1066,13 +1057,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C48" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1343.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="49">
@@ -1080,13 +1071,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C49" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1379.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="50">
@@ -1094,13 +1085,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C50" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1723.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="51">
@@ -1108,13 +1099,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C51" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1552.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="52">
@@ -1122,13 +1113,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C52" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1408.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="53">
@@ -1142,7 +1133,7 @@
         <v>102.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1468.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="54">
@@ -1156,7 +1147,7 @@
         <v>102.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1477.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="55">
@@ -1170,7 +1161,7 @@
         <v>102.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1447.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="56">
@@ -1184,7 +1175,7 @@
         <v>102.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1252.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="57">
@@ -1192,13 +1183,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1248.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="58">
@@ -1206,13 +1197,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1316.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="59">
@@ -1220,13 +1211,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1305.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="60">
@@ -1234,13 +1225,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1284.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="61">
@@ -1248,13 +1239,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C61" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1392.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="62">
@@ -1262,13 +1253,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>310.0</v>
+        <v>307.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1246.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="63">
@@ -1276,13 +1267,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1146.0</v>
+        <v>1047.0</v>
       </c>
     </row>
     <row r="64">
@@ -1290,13 +1281,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>985.0</v>
+        <v>1043.0</v>
       </c>
     </row>
     <row r="65">
@@ -1304,13 +1295,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1036.0</v>
+        <v>948.0</v>
       </c>
     </row>
     <row r="66">
@@ -1318,13 +1309,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>308.0</v>
+        <v>300.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1067.0</v>
+        <v>1196.0</v>
       </c>
     </row>
     <row r="67">
@@ -1332,13 +1323,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1023.0</v>
+        <v>1123.0</v>
       </c>
     </row>
     <row r="68">
@@ -1346,13 +1337,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1021.0</v>
+        <v>1192.0</v>
       </c>
     </row>
     <row r="69">
@@ -1360,13 +1351,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1047.0</v>
+        <v>1136.0</v>
       </c>
     </row>
     <row r="70">
@@ -1380,7 +1371,7 @@
         <v>100.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1043.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="71">
@@ -1394,7 +1385,7 @@
         <v>100.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>948.0</v>
+        <v>1006.0</v>
       </c>
     </row>
     <row r="72">
@@ -1408,7 +1399,7 @@
         <v>100.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1196.0</v>
+        <v>1074.0</v>
       </c>
     </row>
     <row r="73">
@@ -1422,7 +1413,7 @@
         <v>100.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1123.0</v>
+        <v>974.0</v>
       </c>
     </row>
     <row r="74">
@@ -1436,7 +1427,7 @@
         <v>100.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1192.0</v>
+        <v>945.0</v>
       </c>
     </row>
     <row r="75">
@@ -1450,7 +1441,7 @@
         <v>100.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1136.0</v>
+        <v>1046.0</v>
       </c>
     </row>
     <row r="76">
@@ -1464,7 +1455,7 @@
         <v>100.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>980.0</v>
+        <v>1105.0</v>
       </c>
     </row>
     <row r="77">
@@ -1472,13 +1463,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1006.0</v>
+        <v>861.0</v>
       </c>
     </row>
     <row r="78">
@@ -1486,13 +1477,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1074.0</v>
+        <v>938.0</v>
       </c>
     </row>
     <row r="79">
@@ -1500,13 +1491,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>974.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="80">
@@ -1514,13 +1505,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>945.0</v>
+        <v>935.0</v>
       </c>
     </row>
     <row r="81">
@@ -1528,13 +1519,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1046.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="82">
@@ -1542,13 +1533,13 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>300.0</v>
+        <v>295.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1105.0</v>
+        <v>1014.0</v>
       </c>
     </row>
     <row r="83">
@@ -1556,13 +1547,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>861.0</v>
+        <v>926.0</v>
       </c>
     </row>
     <row r="84">
@@ -1570,55 +1561,13 @@
         <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>938.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>294.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>103.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
-        <v>950.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>294.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>103.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>935.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>294.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>103.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>950.0</v>
+        <v>1052.0</v>
       </c>
     </row>
   </sheetData>
@@ -1633,27 +1582,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>113.0</v>
@@ -1661,13 +1610,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1675,13 +1624,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>10.0</v>
@@ -1689,13 +1638,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>8.0</v>
@@ -1703,13 +1652,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1717,27 +1666,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1745,13 +1694,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D9" t="n" s="0">
         <v>36.0</v>
@@ -1769,16 +1718,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1793,18 +1742,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,15 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -279,6 +270,18 @@
   </si>
   <si>
     <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>2026-10-13</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
+    <t>2026-10-16</t>
   </si>
   <si>
     <t>Reason</t>
@@ -391,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -412,47 +415,47 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>305.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>132.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1497.0</v>
+        <v>1575.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>329.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>112.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1499.0</v>
+        <v>1574.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>305.0</v>
+        <v>329.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>132.0</v>
+        <v>112.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1575.0</v>
+        <v>1697.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
         <v>329.0</v>
@@ -461,12 +464,12 @@
         <v>112.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1574.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
         <v>329.0</v>
@@ -475,12 +478,12 @@
         <v>112.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1697.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
         <v>329.0</v>
@@ -489,12 +492,12 @@
         <v>112.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1657.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
         <v>329.0</v>
@@ -503,12 +506,12 @@
         <v>112.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1598.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
         <v>329.0</v>
@@ -517,12 +520,12 @@
         <v>112.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1588.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
         <v>329.0</v>
@@ -531,12 +534,12 @@
         <v>112.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1650.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>329.0</v>
@@ -545,12 +548,12 @@
         <v>112.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1619.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>329.0</v>
@@ -559,12 +562,12 @@
         <v>112.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1890.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>329.0</v>
@@ -573,12 +576,12 @@
         <v>112.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>1849.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>329.0</v>
@@ -587,68 +590,68 @@
         <v>112.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1497.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1558.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1472.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>105.0</v>
+        <v>102.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1458.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>105.0</v>
+        <v>102.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1557.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
         <v>335.0</v>
@@ -657,40 +660,40 @@
         <v>102.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1396.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1670.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1546.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
         <v>332.0</v>
@@ -699,12 +702,12 @@
         <v>101.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1531.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
         <v>332.0</v>
@@ -713,40 +716,40 @@
         <v>101.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1389.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1282.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1293.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
         <v>330.0</v>
@@ -755,40 +758,40 @@
         <v>101.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1307.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1414.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1308.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
         <v>331.0</v>
@@ -797,12 +800,12 @@
         <v>100.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1305.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
         <v>331.0</v>
@@ -811,40 +814,40 @@
         <v>100.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1237.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C31" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1199.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C32" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1369.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>329.0</v>
@@ -853,12 +856,12 @@
         <v>100.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1467.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>329.0</v>
@@ -867,12 +870,12 @@
         <v>100.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1472.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
         <v>329.0</v>
@@ -881,12 +884,12 @@
         <v>100.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1259.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
         <v>329.0</v>
@@ -895,12 +898,12 @@
         <v>100.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1254.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
         <v>329.0</v>
@@ -909,40 +912,40 @@
         <v>100.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1326.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1313.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1391.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>319.0</v>
@@ -951,12 +954,12 @@
         <v>102.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1431.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>319.0</v>
@@ -965,12 +968,12 @@
         <v>102.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1493.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>319.0</v>
@@ -979,12 +982,12 @@
         <v>102.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1343.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>319.0</v>
@@ -993,12 +996,12 @@
         <v>102.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1379.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>319.0</v>
@@ -1007,40 +1010,40 @@
         <v>102.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1723.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C45" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1552.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C46" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1408.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>310.0</v>
@@ -1049,12 +1052,12 @@
         <v>102.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1468.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>310.0</v>
@@ -1063,12 +1066,12 @@
         <v>102.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1477.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>310.0</v>
@@ -1077,12 +1080,12 @@
         <v>102.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1447.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>310.0</v>
@@ -1091,12 +1094,12 @@
         <v>102.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1252.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>310.0</v>
@@ -1105,12 +1108,12 @@
         <v>102.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1248.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>310.0</v>
@@ -1119,12 +1122,12 @@
         <v>102.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1316.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>310.0</v>
@@ -1133,12 +1136,12 @@
         <v>102.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1305.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>310.0</v>
@@ -1147,40 +1150,40 @@
         <v>102.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1284.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1392.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1246.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>308.0</v>
@@ -1189,12 +1192,12 @@
         <v>101.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1146.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>308.0</v>
@@ -1203,40 +1206,40 @@
         <v>101.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>985.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1036.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1067.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>307.0</v>
@@ -1245,40 +1248,40 @@
         <v>102.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1023.0</v>
+        <v>1047.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1021.0</v>
+        <v>1043.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1047.0</v>
+        <v>948.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>300.0</v>
@@ -1287,12 +1290,12 @@
         <v>100.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1043.0</v>
+        <v>1196.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>300.0</v>
@@ -1301,12 +1304,12 @@
         <v>100.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>948.0</v>
+        <v>1123.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>300.0</v>
@@ -1315,12 +1318,12 @@
         <v>100.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1196.0</v>
+        <v>1192.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>300.0</v>
@@ -1329,12 +1332,12 @@
         <v>100.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1123.0</v>
+        <v>1136.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>300.0</v>
@@ -1343,12 +1346,12 @@
         <v>100.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1192.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>300.0</v>
@@ -1357,12 +1360,12 @@
         <v>100.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1136.0</v>
+        <v>1006.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>300.0</v>
@@ -1371,12 +1374,12 @@
         <v>100.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>980.0</v>
+        <v>1074.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>300.0</v>
@@ -1385,12 +1388,12 @@
         <v>100.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1006.0</v>
+        <v>974.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>300.0</v>
@@ -1399,12 +1402,12 @@
         <v>100.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1074.0</v>
+        <v>945.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>300.0</v>
@@ -1413,12 +1416,12 @@
         <v>100.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>974.0</v>
+        <v>1046.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>300.0</v>
@@ -1427,40 +1430,40 @@
         <v>100.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>945.0</v>
+        <v>1105.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1046.0</v>
+        <v>861.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1105.0</v>
+        <v>938.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
         <v>294.0</v>
@@ -1469,12 +1472,12 @@
         <v>103.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>861.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
         <v>294.0</v>
@@ -1483,12 +1486,12 @@
         <v>103.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>938.0</v>
+        <v>935.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
         <v>294.0</v>
@@ -1502,35 +1505,35 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>935.0</v>
+        <v>1014.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>950.0</v>
+        <v>926.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
         <v>295.0</v>
@@ -1539,35 +1542,63 @@
         <v>101.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1014.0</v>
+        <v>1052.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>295.0</v>
+        <v>290.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>101.0</v>
+        <v>98.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>926.0</v>
+        <v>1057.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>290.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>98.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>1025.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="B84" t="n" s="0">
-        <v>295.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>101.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
-        <v>1052.0</v>
+      <c r="B85" t="n" s="0">
+        <v>290.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>98.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>937.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>290.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>98.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>957.0</v>
       </c>
     </row>
   </sheetData>
@@ -1582,41 +1613,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>113.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>94</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1624,27 +1655,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>8.0</v>
@@ -1652,13 +1683,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1666,27 +1697,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>100.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1694,16 +1725,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>36.0</v>
+        <v>30.0</v>
       </c>
     </row>
   </sheetData>
@@ -1718,16 +1749,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1742,18 +1773,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export/Coverage.xlsx
+++ b/gsc-export/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,18 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>2026-07-26</t>
-  </si>
-  <si>
     <t>2026-07-27</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-07-28</t>
   </si>
   <si>
@@ -282,6 +276,15 @@
   </si>
   <si>
     <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-17</t>
+  </si>
+  <si>
+    <t>2026-10-18</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
   </si>
   <si>
     <t>Reason</t>
@@ -415,131 +418,131 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>305.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>132.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1575.0</v>
+        <v>1657.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>112.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1574.0</v>
+        <v>1598.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>112.0</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1697.0</v>
+        <v>1588.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B5" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>112.0</v>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1657.0</v>
+        <v>1650.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B6" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>112.0</v>
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1598.0</v>
+        <v>1619.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B7" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>112.0</v>
+        <v>10</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1588.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B8" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C8" t="n" s="0">
-        <v>112.0</v>
+        <v>11</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1650.0</v>
+        <v>1849.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B9" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C9" t="n" s="0">
-        <v>112.0</v>
+        <v>12</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>1619.0</v>
+        <v>1497.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B10" t="n" s="0">
-        <v>329.0</v>
-      </c>
-      <c r="C10" t="n" s="0">
-        <v>112.0</v>
+        <v>13</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1890.0</v>
+        <v>1558.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
         <v>329.0</v>
@@ -548,124 +551,124 @@
         <v>112.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1849.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1497.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
         <v>329.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>112.0</v>
+        <v>105.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>1558.0</v>
+        <v>1557.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>112.0</v>
+        <v>102.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1472.0</v>
+        <v>1396.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>105.0</v>
+        <v>102.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>1458.0</v>
+        <v>1670.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>329.0</v>
+        <v>335.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>105.0</v>
+        <v>102.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1557.0</v>
+        <v>1546.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>1396.0</v>
+        <v>1531.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1670.0</v>
+        <v>1389.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>335.0</v>
+        <v>332.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1546.0</v>
+        <v>1282.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
         <v>332.0</v>
@@ -674,96 +677,96 @@
         <v>101.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1531.0</v>
+        <v>1293.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>1389.0</v>
+        <v>1307.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1282.0</v>
+        <v>1414.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>332.0</v>
+        <v>330.0</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>101.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1293.0</v>
+        <v>1308.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1307.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>1414.0</v>
+        <v>1237.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>101.0</v>
+        <v>100.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1308.0</v>
+        <v>1199.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
         <v>331.0</v>
@@ -772,54 +775,54 @@
         <v>100.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1305.0</v>
+        <v>1369.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1237.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C29" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1199.0</v>
+        <v>1472.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>331.0</v>
+        <v>329.0</v>
       </c>
       <c r="C30" t="n" s="0">
         <v>100.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1369.0</v>
+        <v>1259.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
         <v>329.0</v>
@@ -828,12 +831,12 @@
         <v>100.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1467.0</v>
+        <v>1254.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
         <v>329.0</v>
@@ -842,12 +845,12 @@
         <v>100.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1472.0</v>
+        <v>1326.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>329.0</v>
@@ -856,12 +859,12 @@
         <v>100.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1259.0</v>
+        <v>1313.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
         <v>329.0</v>
@@ -870,54 +873,54 @@
         <v>100.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1254.0</v>
+        <v>1391.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1326.0</v>
+        <v>1431.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1313.0</v>
+        <v>1493.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>329.0</v>
+        <v>319.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1391.0</v>
+        <v>1343.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>319.0</v>
@@ -926,12 +929,12 @@
         <v>102.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1431.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>319.0</v>
@@ -940,12 +943,12 @@
         <v>102.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1493.0</v>
+        <v>1723.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>319.0</v>
@@ -954,12 +957,12 @@
         <v>102.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1343.0</v>
+        <v>1552.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>319.0</v>
@@ -968,54 +971,54 @@
         <v>102.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1379.0</v>
+        <v>1408.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C42" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>1723.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C43" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>1552.0</v>
+        <v>1477.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>319.0</v>
+        <v>310.0</v>
       </c>
       <c r="C44" t="n" s="0">
         <v>102.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>1408.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>310.0</v>
@@ -1024,12 +1027,12 @@
         <v>102.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>1468.0</v>
+        <v>1252.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>310.0</v>
@@ -1038,12 +1041,12 @@
         <v>102.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>1477.0</v>
+        <v>1248.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
         <v>310.0</v>
@@ -1052,12 +1055,12 @@
         <v>102.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>1447.0</v>
+        <v>1316.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
         <v>310.0</v>
@@ -1066,12 +1069,12 @@
         <v>102.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>1252.0</v>
+        <v>1305.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
         <v>310.0</v>
@@ -1080,12 +1083,12 @@
         <v>102.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>1248.0</v>
+        <v>1284.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
         <v>310.0</v>
@@ -1094,12 +1097,12 @@
         <v>102.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1316.0</v>
+        <v>1392.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
         <v>310.0</v>
@@ -1108,54 +1111,54 @@
         <v>102.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>1305.0</v>
+        <v>1246.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1284.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1392.0</v>
+        <v>985.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>310.0</v>
+        <v>308.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>102.0</v>
+        <v>101.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1246.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>308.0</v>
@@ -1164,96 +1167,96 @@
         <v>101.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1146.0</v>
+        <v>1067.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>985.0</v>
+        <v>1023.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1036.0</v>
+        <v>1021.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>308.0</v>
+        <v>307.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1067.0</v>
+        <v>1047.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1023.0</v>
+        <v>1043.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1021.0</v>
+        <v>948.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>307.0</v>
+        <v>300.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>102.0</v>
+        <v>100.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1047.0</v>
+        <v>1196.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
         <v>300.0</v>
@@ -1262,12 +1265,12 @@
         <v>100.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>1043.0</v>
+        <v>1123.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>300.0</v>
@@ -1276,12 +1279,12 @@
         <v>100.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>948.0</v>
+        <v>1192.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>300.0</v>
@@ -1290,12 +1293,12 @@
         <v>100.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>1196.0</v>
+        <v>1136.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>300.0</v>
@@ -1304,12 +1307,12 @@
         <v>100.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>1123.0</v>
+        <v>980.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>300.0</v>
@@ -1318,12 +1321,12 @@
         <v>100.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1192.0</v>
+        <v>1006.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>300.0</v>
@@ -1332,12 +1335,12 @@
         <v>100.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>1136.0</v>
+        <v>1074.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>300.0</v>
@@ -1346,12 +1349,12 @@
         <v>100.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>980.0</v>
+        <v>974.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>300.0</v>
@@ -1360,12 +1363,12 @@
         <v>100.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1006.0</v>
+        <v>945.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>300.0</v>
@@ -1374,12 +1377,12 @@
         <v>100.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1074.0</v>
+        <v>1046.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>300.0</v>
@@ -1388,54 +1391,54 @@
         <v>100.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>974.0</v>
+        <v>1105.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>945.0</v>
+        <v>861.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1046.0</v>
+        <v>938.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>300.0</v>
+        <v>294.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1105.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
         <v>294.0</v>
@@ -1444,12 +1447,12 @@
         <v>103.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>861.0</v>
+        <v>935.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
         <v>294.0</v>
@@ -1458,96 +1461,96 @@
         <v>103.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>938.0</v>
+        <v>950.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>950.0</v>
+        <v>1014.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>935.0</v>
+        <v>926.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>103.0</v>
+        <v>101.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>950.0</v>
+        <v>1052.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>295.0</v>
+        <v>290.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>101.0</v>
+        <v>98.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1014.0</v>
+        <v>1057.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>295.0</v>
+        <v>290.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>101.0</v>
+        <v>98.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>926.0</v>
+        <v>1025.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>295.0</v>
+        <v>290.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>101.0</v>
+        <v>98.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1052.0</v>
+        <v>937.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
         <v>290.0</v>
@@ -1556,49 +1559,49 @@
         <v>98.0</v>
       </c>
       <c r="D83" t="n" s="0">
-        <v>1057.0</v>
+        <v>957.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>290.0</v>
+        <v>285.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1025.0</v>
+        <v>1095.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>290.0</v>
+        <v>285.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>937.0</v>
+        <v>1022.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>290.0</v>
+        <v>285.0</v>
       </c>
       <c r="C86" t="n" s="0">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>957.0</v>
+        <v>989.0</v>
       </c>
     </row>
   </sheetData>
@@ -1613,41 +1616,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>116.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>25.0</v>
@@ -1655,13 +1658,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>11.0</v>
@@ -1669,27 +1672,27 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>3.0</v>
@@ -1697,27 +1700,27 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>97.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" t="n" s="0">
         <v>0.0</v>
@@ -1725,16 +1728,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>30.0</v>
+        <v>28.0</v>
       </c>
     </row>
   </sheetData>
@@ -1749,16 +1752,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1773,18 +1776,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
